--- a/data/trans_orig/Q64D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar</t>
+          <t>Número medio de minutos que utilizan en todos sus desplazamientos para ir a trabajar (tasa de respuesta: 88,38%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 11,91</t>
+          <t>6,28; 11,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,06; 12,53</t>
+          <t>5,92; 11,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 15,86</t>
+          <t>7,56; 16,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,4; 30,8</t>
+          <t>10,72; 29,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 15,83</t>
+          <t>8,05; 15,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 9,12</t>
+          <t>4,3; 9,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,05; 13,66</t>
+          <t>3,0; 12,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,52; 51,76</t>
+          <t>12,76; 48,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,37; 11,86</t>
+          <t>7,3; 11,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 9,91</t>
+          <t>5,72; 9,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,79</t>
+          <t>6,78; 12,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,03; 32,08</t>
+          <t>13,17; 32,91</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,25; 12,14</t>
+          <t>8,3; 12,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 11,16</t>
+          <t>7,46; 10,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,29</t>
+          <t>7,46; 11,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,82; 19,39</t>
+          <t>7,78; 19,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,33; 8,07</t>
+          <t>5,25; 8,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,71; 10,21</t>
+          <t>6,8; 10,34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,63; 10,01</t>
+          <t>6,78; 10,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,53; 16,59</t>
+          <t>10,29; 16,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,64; 10,35</t>
+          <t>7,57; 10,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,04</t>
+          <t>7,44; 9,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,15</t>
+          <t>7,63; 10,24</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,06; 17,16</t>
+          <t>9,09; 17,22</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,02; 15,37</t>
+          <t>9,38; 15,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,99</t>
+          <t>6,84; 11,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,51; 15,48</t>
+          <t>9,5; 15,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,93; 24,06</t>
+          <t>15,22; 23,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 14,55</t>
+          <t>8,76; 14,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,27; 13,34</t>
+          <t>7,29; 13,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,54; 20,4</t>
+          <t>12,13; 20,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,23; 21,58</t>
+          <t>14,46; 21,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,8; 13,96</t>
+          <t>9,77; 13,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,96; 11,82</t>
+          <t>7,59; 11,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,44; 16,26</t>
+          <t>11,6; 16,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,92; 21,88</t>
+          <t>15,9; 21,36</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,71; 11,53</t>
+          <t>8,67; 11,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,73; 10,44</t>
+          <t>7,75; 10,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,63; 11,47</t>
+          <t>8,76; 11,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 19,35</t>
+          <t>9,7; 19,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,39; 9,9</t>
+          <t>7,29; 9,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,27; 9,96</t>
+          <t>7,35; 9,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,18</t>
+          <t>8,91; 11,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,79; 17,99</t>
+          <t>13,09; 17,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 10,64</t>
+          <t>8,46; 10,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,82; 9,81</t>
+          <t>7,74; 9,69</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,16; 11,35</t>
+          <t>9,13; 11,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,78; 17,82</t>
+          <t>11,68; 17,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64D_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q64D_R-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16,39</t>
+          <t>15,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>23,56</t>
+          <t>15,01</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,26</t>
+          <t>15,42</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,28; 11,65</t>
+          <t>6,19; 11,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,92; 11,78</t>
+          <t>5,77; 12,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 16,03</t>
+          <t>7,84; 16,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,72; 29,94</t>
+          <t>10,63; 27,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,05; 15,92</t>
+          <t>8,01; 15,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,3; 9,36</t>
+          <t>4,42; 9,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,63</t>
+          <t>3,04; 13,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 48,46</t>
+          <t>10,13; 22,87</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,3; 11,67</t>
+          <t>7,33; 11,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,72; 9,85</t>
+          <t>5,75; 9,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,78; 12,94</t>
+          <t>6,53; 12,63</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,17; 32,91</t>
+          <t>11,33; 22,54</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,61</t>
+          <t>18,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>16,45</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,44</t>
+          <t>17,86</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,23</t>
+          <t>8,21; 12,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 10,95</t>
+          <t>7,35; 10,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,46; 11,27</t>
+          <t>7,48; 11,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,78; 19,52</t>
+          <t>16,95; 21,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,09</t>
+          <t>5,16; 7,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,8; 10,34</t>
+          <t>6,76; 10,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,78; 10,01</t>
+          <t>6,89; 10,06</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,29; 16,48</t>
+          <t>14,6; 18,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 10,34</t>
+          <t>7,62; 10,33</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 9,95</t>
+          <t>7,52; 10,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,24</t>
+          <t>7,62; 10,26</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,09; 17,22</t>
+          <t>16,57; 19,47</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,04</t>
+          <t>17,55</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,7</t>
+          <t>17,71</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>18,36</t>
+          <t>17,63</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,38; 15,57</t>
+          <t>9,27; 15,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,84; 11,89</t>
+          <t>6,93; 12,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9,5; 15,14</t>
+          <t>9,4; 15,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,22; 23,87</t>
+          <t>14,2; 21,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 14,84</t>
+          <t>8,63; 14,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 13,0</t>
+          <t>7,38; 13,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,13; 20,0</t>
+          <t>12,39; 19,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 21,83</t>
+          <t>14,71; 21,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,77; 13,9</t>
+          <t>9,8; 13,73</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,59; 11,51</t>
+          <t>7,82; 11,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11,6; 16,46</t>
+          <t>11,86; 16,36</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,9; 21,36</t>
+          <t>14,96; 20,22</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,7</t>
+          <t>18,34</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>15,72</t>
+          <t>16,77</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,71</t>
+          <t>17,63</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 11,53</t>
+          <t>8,81; 11,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,45</t>
+          <t>7,67; 10,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 11,74</t>
+          <t>8,6; 11,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,7; 19,33</t>
+          <t>16,47; 20,24</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,89</t>
+          <t>7,32; 9,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 9,95</t>
+          <t>7,25; 9,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,91; 11,97</t>
+          <t>8,89; 12,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,09; 17,98</t>
+          <t>15,15; 18,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,46; 10,52</t>
+          <t>8,59; 10,51</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 9,69</t>
+          <t>7,76; 9,78</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,13; 11,27</t>
+          <t>9,15; 11,37</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 17,89</t>
+          <t>16,48; 18,97</t>
         </is>
       </c>
     </row>
